--- a/Codebooks/Human Codebooks/content - cleaned/F - Content Analysis Codebook (cleaned) - KK.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/F - Content Analysis Codebook (cleaned) - KK.xlsx
@@ -677,7 +677,7 @@
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>From a conversation “There’s no difference between a man who lies about his feelings and a woman who lies about cuming!”</t>
+          <t>From a conversation "There's no difference between a man who lies about his feelings and a woman who lies about cuming!"</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr"/>
@@ -927,7 +927,7 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Religion/morality</t>
+          <t>Religion/morality, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Social issues, gender issues</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>Cultura/social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Stories about men/women</t>
+          <t>Stories about men/women, Personal experience</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
@@ -2252,13 +2252,13 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr"/>
@@ -2322,7 +2322,7 @@
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>References religion/tradition, Presented as common sense</t>
+          <t>Presented as common sense, References religion/tradition</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -2643,7 +2643,7 @@
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
@@ -2774,7 +2774,7 @@
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>Calls for reading the influencer's content with an open mind</t>
+          <t>Calls for audience to take action in their own life</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>Stories about men/women, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Stories about men/women</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>Calls for women to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr"/>
@@ -3720,12 +3720,12 @@
       <c r="U26" s="3" t="inlineStr"/>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>Stories about men/women, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Stories about men/women</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -4101,7 +4101,7 @@
       <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Other</t>
+          <t>Other, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
       <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4676,7 +4676,7 @@
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>Stories about men/women, Cultural/social observations</t>
+          <t>Cultural/social observations, Stories about men/women</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
@@ -4797,7 +4797,7 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Family/children, gender issues</t>
+          <t>Family/children, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -4973,13 +4973,13 @@
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -5094,7 +5094,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -5149,12 +5149,12 @@
       <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Stories about men/women</t>
+          <t>Stories about men/women, Personal experience</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
@@ -5619,7 +5619,7 @@
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr"/>
@@ -5734,7 +5734,7 @@
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -5857,7 +5857,7 @@
       <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
@@ -6052,7 +6052,7 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Mental health, gender issues, Other</t>
+          <t>Mental health, Other, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -6103,7 +6103,7 @@
       <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Men need to be more emotionally open</t>
+          <t>Men need to be emotionally open</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr"/>
@@ -6226,7 +6226,7 @@
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -6349,7 +6349,7 @@
       <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -6472,7 +6472,7 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr"/>
@@ -6591,7 +6591,7 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Information seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
@@ -6802,7 +6802,7 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Family/children, gender issues, Other</t>
+          <t>Family/children, Other, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -6857,7 +6857,7 @@
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
@@ -6925,7 +6925,7 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Social issues</t>
+          <t>Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
@@ -7040,7 +7040,7 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Social issues</t>
+          <t>Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Social issues</t>
+          <t>Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
       <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -7575,7 +7575,7 @@
       <c r="U19" s="3" t="inlineStr"/>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
@@ -7702,7 +7702,7 @@
       <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -7770,7 +7770,7 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -7825,7 +7825,7 @@
       <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
@@ -7893,13 +7893,13 @@
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -8028,13 +8028,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -8079,7 +8079,7 @@
       <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -8155,13 +8155,13 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -8206,7 +8206,7 @@
       <c r="U24" s="3" t="inlineStr"/>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -8274,13 +8274,13 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues, Money/status</t>
+          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -8327,13 +8327,13 @@
       <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -8413,7 +8413,7 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
@@ -8466,13 +8466,13 @@
       <c r="S26" s="3" t="inlineStr"/>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr"/>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -8552,13 +8552,13 @@
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
@@ -8599,19 +8599,19 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>More self-discipline/fitness, More equality/respect for men</t>
+          <t>More equality/respect for men, More self-discipline/fitness</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr"/>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -8679,13 +8679,13 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -8732,13 +8732,13 @@
       <c r="S28" s="3" t="inlineStr"/>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -8749,7 +8749,7 @@
       <c r="X28" s="3" t="inlineStr"/>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>Presented as common sense, References religion/tradition, Other</t>
+          <t>References religion/tradition, Presented as common sense, Other</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, calls for women to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr"/>
@@ -8818,13 +8818,13 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -8867,13 +8867,13 @@
       <c r="S29" s="3" t="inlineStr"/>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -8949,13 +8949,13 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
@@ -9002,13 +9002,13 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -9076,13 +9076,13 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -9129,13 +9129,13 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -9211,7 +9211,7 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
@@ -9258,19 +9258,19 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More equality/respect for men</t>
+          <t>More equality/respect for men, Assert dominance/control</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -9346,13 +9346,13 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -9389,19 +9389,19 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More equality/respect for men</t>
+          <t>More equality/respect for men, Assert dominance/control</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr"/>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>
@@ -9699,13 +9699,13 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
@@ -9748,7 +9748,7 @@
       <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
@@ -9834,13 +9834,13 @@
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
@@ -9892,7 +9892,7 @@
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
@@ -9949,13 +9949,13 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Gender issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Interview/conversational content</t>
+          <t>Interview/conversational content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -10199,13 +10199,13 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Dating/marriage</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>Assert dominance/control, More equality/respect for men</t>
+          <t>More equality/respect for men, Assert dominance/control</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Commentary/reaction content, Motivational/self-help content</t>
+          <t>Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr"/>

--- a/Codebooks/Human Codebooks/content - cleaned/F - Content Analysis Codebook (cleaned) - KK.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/F - Content Analysis Codebook (cleaned) - KK.xlsx
@@ -897,7 +897,7 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for women to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr"/>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr"/>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr"/>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms, calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr"/>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr"/>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">

--- a/Codebooks/Human Codebooks/content - cleaned/F - Content Analysis Codebook (cleaned) - KK.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/F - Content Analysis Codebook (cleaned) - KK.xlsx
@@ -450,42 +450,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>Calls for audience to take action in their own life</t>
+          <t>Calls for reading the influencer's content with an open mind</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr"/>
@@ -5206,42 +5206,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
